--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/62.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/62.xlsx
@@ -426,13 +426,13 @@
         <v>-2.732231212945175</v>
       </c>
       <c r="E2">
-        <v>-16.05374131318353</v>
+        <v>-12.53258559225337</v>
       </c>
       <c r="F2">
-        <v>-4.041003663335609</v>
+        <v>-4.004723336371764</v>
       </c>
       <c r="G2">
-        <v>-6.02662418781486</v>
+        <v>-3.905726498626313</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.432807992910432</v>
       </c>
       <c r="E3">
-        <v>-14.84216167785334</v>
+        <v>-12.22006654403602</v>
       </c>
       <c r="F3">
-        <v>-4.58249884697196</v>
+        <v>-4.620056432756607</v>
       </c>
       <c r="G3">
-        <v>-3.451238254267468</v>
+        <v>-3.315191385331119</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.155574380911739</v>
       </c>
       <c r="E4">
-        <v>-14.06905153831585</v>
+        <v>-14.51891467471183</v>
       </c>
       <c r="F4">
-        <v>-5.060785951964251</v>
+        <v>-4.660395797981723</v>
       </c>
       <c r="G4">
-        <v>-4.231742402242661</v>
+        <v>-2.1661440657421</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.912245703337228</v>
       </c>
       <c r="E5">
-        <v>-15.25598268962228</v>
+        <v>-12.82431894477551</v>
       </c>
       <c r="F5">
-        <v>-4.799384996532519</v>
+        <v>-4.417864698532453</v>
       </c>
       <c r="G5">
-        <v>-3.711728530025021</v>
+        <v>-2.233861274747892</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-1.686865911302097</v>
       </c>
       <c r="E6">
-        <v>-17.41793957952021</v>
+        <v>-14.25921121884594</v>
       </c>
       <c r="F6">
-        <v>-4.475928108510209</v>
+        <v>-4.854212103472076</v>
       </c>
       <c r="G6">
-        <v>-4.26377193033511</v>
+        <v>-1.668231395544635</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.471057120724334</v>
       </c>
       <c r="E7">
-        <v>-17.41876376178961</v>
+        <v>-15.2913591285702</v>
       </c>
       <c r="F7">
-        <v>-4.32486552791306</v>
+        <v>-4.815473864927469</v>
       </c>
       <c r="G7">
-        <v>-3.909858059459323</v>
+        <v>-2.940887864478961</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.251459740288428</v>
       </c>
       <c r="E8">
-        <v>-18.67056983172992</v>
+        <v>-16.13863208693131</v>
       </c>
       <c r="F8">
-        <v>-4.544082100728188</v>
+        <v>-4.228143064686469</v>
       </c>
       <c r="G8">
-        <v>-2.495268571619824</v>
+        <v>-2.084681471657254</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.017430778156698</v>
       </c>
       <c r="E9">
-        <v>-19.25312178502466</v>
+        <v>-17.64425459652755</v>
       </c>
       <c r="F9">
-        <v>-4.800873680093033</v>
+        <v>-4.249779654903202</v>
       </c>
       <c r="G9">
-        <v>-2.39853112041678</v>
+        <v>-2.538378495632213</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.7594959014458013</v>
       </c>
       <c r="E10">
-        <v>-19.67732658769318</v>
+        <v>-19.81308570996913</v>
       </c>
       <c r="F10">
-        <v>-3.855727491994263</v>
+        <v>-4.03759632005854</v>
       </c>
       <c r="G10">
-        <v>-2.915492669647212</v>
+        <v>-0.7592019380983167</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.470272597369799</v>
       </c>
       <c r="E11">
-        <v>-22.38439853626443</v>
+        <v>-19.91935088103312</v>
       </c>
       <c r="F11">
-        <v>-4.071848711597665</v>
+        <v>-3.974490390446025</v>
       </c>
       <c r="G11">
-        <v>-1.993833480968574</v>
+        <v>-0.8435877438943392</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.1466286558170005</v>
       </c>
       <c r="E12">
-        <v>-21.05531405738322</v>
+        <v>-19.35356786698879</v>
       </c>
       <c r="F12">
-        <v>-4.242839855581747</v>
+        <v>-3.949328470861523</v>
       </c>
       <c r="G12">
-        <v>-1.908914677340729</v>
+        <v>-1.241419311894097</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.2107425970199658</v>
       </c>
       <c r="E13">
-        <v>-21.91824647886286</v>
+        <v>-18.78746333128992</v>
       </c>
       <c r="F13">
-        <v>-4.173633490782958</v>
+        <v>-3.958735683999234</v>
       </c>
       <c r="G13">
-        <v>-2.147230919076244</v>
+        <v>-1.011571445648038</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.5948243389462056</v>
       </c>
       <c r="E14">
-        <v>-21.40526547174797</v>
+        <v>-20.00075925826901</v>
       </c>
       <c r="F14">
-        <v>-3.666695562074453</v>
+        <v>-4.585236282646798</v>
       </c>
       <c r="G14">
-        <v>-1.032858253465551</v>
+        <v>-0.6550323121596096</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.9955890554992791</v>
       </c>
       <c r="E15">
-        <v>-23.0496857096793</v>
+        <v>-22.76882975172358</v>
       </c>
       <c r="F15">
-        <v>-3.701320124503706</v>
+        <v>-3.584514686563427</v>
       </c>
       <c r="G15">
-        <v>-1.054403283835128</v>
+        <v>1.092574883111797</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.398475376094567</v>
       </c>
       <c r="E16">
-        <v>-24.48919249876354</v>
+        <v>-22.09260631358019</v>
       </c>
       <c r="F16">
-        <v>-3.407515754189126</v>
+        <v>-3.166546980625437</v>
       </c>
       <c r="G16">
-        <v>-0.8842710380264429</v>
+        <v>0.1608681887214709</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.788392781595094</v>
       </c>
       <c r="E17">
-        <v>-24.94602042818332</v>
+        <v>-21.65244769698265</v>
       </c>
       <c r="F17">
-        <v>-2.792230960834704</v>
+        <v>-3.51842980612397</v>
       </c>
       <c r="G17">
-        <v>-1.36045990839521</v>
+        <v>3.20962902892925</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.14901381253074</v>
       </c>
       <c r="E18">
-        <v>-25.33534692404477</v>
+        <v>-22.61688133487021</v>
       </c>
       <c r="F18">
-        <v>-3.328257607945043</v>
+        <v>-2.857207247133353</v>
       </c>
       <c r="G18">
-        <v>-0.2479610115597458</v>
+        <v>2.055331184114947</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.465466382275561</v>
       </c>
       <c r="E19">
-        <v>-24.97432791920527</v>
+        <v>-25.31677565213931</v>
       </c>
       <c r="F19">
-        <v>-2.281969625262648</v>
+        <v>-2.986219890269839</v>
       </c>
       <c r="G19">
-        <v>-0.3083586043782093</v>
+        <v>3.067831742391186</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.723636452502217</v>
       </c>
       <c r="E20">
-        <v>-27.65105909192513</v>
+        <v>-25.14431324803119</v>
       </c>
       <c r="F20">
-        <v>-2.774932141120359</v>
+        <v>-2.279303456354006</v>
       </c>
       <c r="G20">
-        <v>0.3443419330534193</v>
+        <v>1.052103463894206</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.914159914749209</v>
       </c>
       <c r="E21">
-        <v>-28.33268047108567</v>
+        <v>-28.67851550257745</v>
       </c>
       <c r="F21">
-        <v>-1.711365135047562</v>
+        <v>-2.973295266293938</v>
       </c>
       <c r="G21">
-        <v>1.177099731820469</v>
+        <v>1.602296269247842</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.031228811553414</v>
       </c>
       <c r="E22">
-        <v>-29.0803632290701</v>
+        <v>-26.25219988553374</v>
       </c>
       <c r="F22">
-        <v>-2.310817620365336</v>
+        <v>-2.212789391611465</v>
       </c>
       <c r="G22">
-        <v>0.5808274431057173</v>
+        <v>1.290105203803491</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.073943693479258</v>
       </c>
       <c r="E23">
-        <v>-28.47031438160079</v>
+        <v>-29.00837860624417</v>
       </c>
       <c r="F23">
-        <v>-1.56504021069645</v>
+        <v>-1.890200374430815</v>
       </c>
       <c r="G23">
-        <v>0.9748750575540882</v>
+        <v>1.655801306253543</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.044556829913546</v>
       </c>
       <c r="E24">
-        <v>-30.1219801779444</v>
+        <v>-27.03578438545098</v>
       </c>
       <c r="F24">
-        <v>-1.031320231251948</v>
+        <v>-1.692241886118631</v>
       </c>
       <c r="G24">
-        <v>-0.451463556404285</v>
+        <v>1.350986136270688</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.950882999880536</v>
       </c>
       <c r="E25">
-        <v>-30.63221692981064</v>
+        <v>-28.82271117192969</v>
       </c>
       <c r="F25">
-        <v>-1.54482262097995</v>
+        <v>-1.155164450133397</v>
       </c>
       <c r="G25">
-        <v>-0.2217183170699431</v>
+        <v>-0.2181892755250801</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.804189903495206</v>
       </c>
       <c r="E26">
-        <v>-31.26767957341099</v>
+        <v>-29.22080479346998</v>
       </c>
       <c r="F26">
-        <v>-1.65812727699415</v>
+        <v>-1.5025155011549</v>
       </c>
       <c r="G26">
-        <v>-1.729115638557371</v>
+        <v>1.122068533321164</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.617918823847227</v>
       </c>
       <c r="E27">
-        <v>-31.94310147165502</v>
+        <v>-29.96357189291908</v>
       </c>
       <c r="F27">
-        <v>-1.663460406664392</v>
+        <v>-0.9586922698228526</v>
       </c>
       <c r="G27">
-        <v>-0.3038430202626435</v>
+        <v>-0.2519767032988818</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.405652107305891</v>
       </c>
       <c r="E28">
-        <v>-30.92850366294749</v>
+        <v>-29.36278603903247</v>
       </c>
       <c r="F28">
-        <v>-1.688619950690021</v>
+        <v>-1.951216604087909</v>
       </c>
       <c r="G28">
-        <v>-1.672528483654609</v>
+        <v>-0.822575711356585</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.18481722002243</v>
       </c>
       <c r="E29">
-        <v>-32.54813276992382</v>
+        <v>-28.26703571187048</v>
       </c>
       <c r="F29">
-        <v>-1.755949623979013</v>
+        <v>-1.484845302403385</v>
       </c>
       <c r="G29">
-        <v>-0.3863351940102029</v>
+        <v>0.09404813755682125</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.972737112710396</v>
       </c>
       <c r="E30">
-        <v>-33.37588121260087</v>
+        <v>-29.52410386860771</v>
       </c>
       <c r="F30">
-        <v>-1.10270260797855</v>
+        <v>-2.458376251624576</v>
       </c>
       <c r="G30">
-        <v>-1.144277974135263</v>
+        <v>-0.779995474630479</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.784763640199899</v>
       </c>
       <c r="E31">
-        <v>-31.63276061943537</v>
+        <v>-28.55794035364922</v>
       </c>
       <c r="F31">
-        <v>-1.517774507650159</v>
+        <v>-2.157309797834748</v>
       </c>
       <c r="G31">
-        <v>-1.417692619678131</v>
+        <v>-0.1561761364834522</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.631350251383013</v>
       </c>
       <c r="E32">
-        <v>-32.05549140381439</v>
+        <v>-28.85757589331474</v>
       </c>
       <c r="F32">
-        <v>-1.265497281997275</v>
+        <v>-1.767056945416948</v>
       </c>
       <c r="G32">
-        <v>-0.8581574548126717</v>
+        <v>1.101771578619892</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.524968244003786</v>
       </c>
       <c r="E33">
-        <v>-32.66263749944478</v>
+        <v>-30.00487836858005</v>
       </c>
       <c r="F33">
-        <v>-1.341756681090473</v>
+        <v>-2.049457841287406</v>
       </c>
       <c r="G33">
-        <v>-0.4867771456716907</v>
+        <v>0.2210969437174316</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.473675975070955</v>
       </c>
       <c r="E34">
-        <v>-33.53586087810685</v>
+        <v>-27.80875414229424</v>
       </c>
       <c r="F34">
-        <v>-1.377207146154627</v>
+        <v>-1.593903251005334</v>
       </c>
       <c r="G34">
-        <v>-0.341887809599948</v>
+        <v>-0.2520230509364316</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.479939636325901</v>
       </c>
       <c r="E35">
-        <v>-30.96992335045865</v>
+        <v>-27.53474976551213</v>
       </c>
       <c r="F35">
-        <v>-1.321415562312569</v>
+        <v>-1.274753251220061</v>
       </c>
       <c r="G35">
-        <v>-1.573519998211625</v>
+        <v>0.7209131775999776</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.540437531209992</v>
       </c>
       <c r="E36">
-        <v>-31.59786646296926</v>
+        <v>-26.8776953578432</v>
       </c>
       <c r="F36">
-        <v>-1.207309551105157</v>
+        <v>-0.8073770881321906</v>
       </c>
       <c r="G36">
-        <v>-0.1924597155938644</v>
+        <v>-0.7729903602693812</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.654321679638456</v>
       </c>
       <c r="E37">
-        <v>-31.02213892000409</v>
+        <v>-30.15254284902216</v>
       </c>
       <c r="F37">
-        <v>-1.04657131921763</v>
+        <v>-1.512165021297673</v>
       </c>
       <c r="G37">
-        <v>0.3505690692127885</v>
+        <v>-0.2790304814458059</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.816009607572008</v>
       </c>
       <c r="E38">
-        <v>-30.46346787438881</v>
+        <v>-27.75797636324623</v>
       </c>
       <c r="F38">
-        <v>-1.319692490276571</v>
+        <v>-1.845184325637407</v>
       </c>
       <c r="G38">
-        <v>-0.07718320937090237</v>
+        <v>0.3206483586288554</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.015849304084404</v>
       </c>
       <c r="E39">
-        <v>-32.61283787078243</v>
+        <v>-29.65016979227024</v>
       </c>
       <c r="F39">
-        <v>-1.704921827530597</v>
+        <v>-0.9088102846042563</v>
       </c>
       <c r="G39">
-        <v>0.4865166217829597</v>
+        <v>0.2191039953027903</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.24129127804708</v>
       </c>
       <c r="E40">
-        <v>-31.64864197778027</v>
+        <v>-26.73857610785356</v>
       </c>
       <c r="F40">
-        <v>-1.297889610938716</v>
+        <v>-1.58208722117024</v>
       </c>
       <c r="G40">
-        <v>-0.6817914517535385</v>
+        <v>0.6542487220756737</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.484611342625818</v>
       </c>
       <c r="E41">
-        <v>-31.59639697315377</v>
+        <v>-26.47836093442481</v>
       </c>
       <c r="F41">
-        <v>-1.822650566019577</v>
+        <v>-1.562758090472302</v>
       </c>
       <c r="G41">
-        <v>-0.8962022441499762</v>
+        <v>-0.626240497604568</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.735496206288692</v>
       </c>
       <c r="E42">
-        <v>-31.37339906335706</v>
+        <v>-25.20843643997981</v>
       </c>
       <c r="F42">
-        <v>-0.8412723539873833</v>
+        <v>-1.646074483124698</v>
       </c>
       <c r="G42">
-        <v>-0.3785752752661513</v>
+        <v>0.3013876046813757</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.9823934493915</v>
       </c>
       <c r="E43">
-        <v>-30.58677369314367</v>
+        <v>-26.15856915695115</v>
       </c>
       <c r="F43">
-        <v>-0.919744982097408</v>
+        <v>-1.395196461648104</v>
       </c>
       <c r="G43">
-        <v>-0.4398931997445322</v>
+        <v>1.739693840764214</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>3.214679741385925</v>
       </c>
       <c r="E44">
-        <v>-29.91449229162395</v>
+        <v>-24.16615833390039</v>
       </c>
       <c r="F44">
-        <v>-1.496487916440738</v>
+        <v>-1.056019708709141</v>
       </c>
       <c r="G44">
-        <v>-1.184527586801722</v>
+        <v>1.427780861145161</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>3.427689486093423</v>
       </c>
       <c r="E45">
-        <v>-28.94153832989096</v>
+        <v>-26.15294026375961</v>
       </c>
       <c r="F45">
-        <v>-0.7906745336950084</v>
+        <v>-1.127075842017163</v>
       </c>
       <c r="G45">
-        <v>0.03473971422077792</v>
+        <v>0.9463017390046385</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>3.616354888967789</v>
       </c>
       <c r="E46">
-        <v>-29.33260375977135</v>
+        <v>-24.69445464010922</v>
       </c>
       <c r="F46">
-        <v>-0.4722213645125289</v>
+        <v>-0.6890758399547793</v>
       </c>
       <c r="G46">
-        <v>-1.06434154154402</v>
+        <v>1.171912106960431</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>3.775279976255369</v>
       </c>
       <c r="E47">
-        <v>-28.68017292406426</v>
+        <v>-23.60764352063837</v>
       </c>
       <c r="F47">
-        <v>-1.329057735207522</v>
+        <v>-2.000050967843442</v>
       </c>
       <c r="G47">
-        <v>-0.9082493193673841</v>
+        <v>1.374888275064226</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>3.901862161654552</v>
       </c>
       <c r="E48">
-        <v>-27.79866923067916</v>
+        <v>-23.79318415768064</v>
       </c>
       <c r="F48">
-        <v>-1.275196688876384</v>
+        <v>-0.6021343444619423</v>
       </c>
       <c r="G48">
-        <v>-1.324401446381469</v>
+        <v>-1.902574982633024</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>3.99871796791616</v>
       </c>
       <c r="E49">
-        <v>-28.82504333604363</v>
+        <v>-22.64713154124145</v>
       </c>
       <c r="F49">
-        <v>-0.7824915252299328</v>
+        <v>-1.913679606480163</v>
       </c>
       <c r="G49">
-        <v>-0.1924464734117073</v>
+        <v>0.6851592857758487</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>4.068008810473348</v>
       </c>
       <c r="E50">
-        <v>-28.26154720137318</v>
+        <v>-23.68195125063023</v>
       </c>
       <c r="F50">
-        <v>-1.49437921201433</v>
+        <v>-1.195430173033445</v>
       </c>
       <c r="G50">
-        <v>-1.783200021032445</v>
+        <v>0.04468459302074857</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>4.110288223610348</v>
       </c>
       <c r="E51">
-        <v>-26.82468504110942</v>
+        <v>-23.01982495207272</v>
       </c>
       <c r="F51">
-        <v>-1.13647038550755</v>
+        <v>-1.078940684423297</v>
       </c>
       <c r="G51">
-        <v>-0.03583449558540524</v>
+        <v>0.8555795490464509</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.128852953737868</v>
       </c>
       <c r="E52">
-        <v>-26.69581372779913</v>
+        <v>-23.41131153003582</v>
       </c>
       <c r="F52">
-        <v>-0.8745103818876687</v>
+        <v>-1.818182931632122</v>
       </c>
       <c r="G52">
-        <v>-0.9267652005685278</v>
+        <v>-0.6248235841137599</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>4.130094628719689</v>
       </c>
       <c r="E53">
-        <v>-26.60467818839477</v>
+        <v>-22.74348388270265</v>
       </c>
       <c r="F53">
-        <v>-1.061619692826135</v>
+        <v>-1.737172414792606</v>
       </c>
       <c r="G53">
-        <v>-0.8462692857811489</v>
+        <v>1.373948080131073</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>4.117674260864719</v>
       </c>
       <c r="E54">
-        <v>-26.06505164021874</v>
+        <v>-20.34492781132596</v>
       </c>
       <c r="F54">
-        <v>-1.18555576665068</v>
+        <v>-0.7837450284620031</v>
       </c>
       <c r="G54">
-        <v>-0.2906273224698729</v>
+        <v>0.1495792284325561</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>4.091426065798609</v>
       </c>
       <c r="E55">
-        <v>-24.49061443960195</v>
+        <v>-21.74781283111018</v>
       </c>
       <c r="F55">
-        <v>-1.054226953612864</v>
+        <v>-1.281483209507721</v>
       </c>
       <c r="G55">
-        <v>-1.64967578779702</v>
+        <v>-0.1124570720918369</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>4.053718210348193</v>
       </c>
       <c r="E56">
-        <v>-26.0195676472857</v>
+        <v>-20.80189612343998</v>
       </c>
       <c r="F56">
-        <v>-0.7661674765065407</v>
+        <v>-0.8435117141518147</v>
       </c>
       <c r="G56">
-        <v>-1.369759230815023</v>
+        <v>-0.3143308285310546</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>4.007851632678111</v>
       </c>
       <c r="E57">
-        <v>-24.30857431296761</v>
+        <v>-20.44804116448062</v>
       </c>
       <c r="F57">
-        <v>-1.140466867385161</v>
+        <v>-1.311890363084158</v>
       </c>
       <c r="G57">
-        <v>-2.505845764617795</v>
+        <v>0.1925534200778354</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>3.953906668584241</v>
       </c>
       <c r="E58">
-        <v>-25.35047655570439</v>
+        <v>-19.27283423238005</v>
       </c>
       <c r="F58">
-        <v>-0.5420738813248166</v>
+        <v>-1.272811627767732</v>
       </c>
       <c r="G58">
-        <v>-1.914231413476798</v>
+        <v>-0.436046345827899</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>3.888283452397313</v>
       </c>
       <c r="E59">
-        <v>-24.19766292757175</v>
+        <v>-19.80536013331204</v>
       </c>
       <c r="F59">
-        <v>-0.8858212095357373</v>
+        <v>-1.45890657506736</v>
       </c>
       <c r="G59">
-        <v>-0.9861994246350635</v>
+        <v>-0.1937442072631016</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>3.812586476857334</v>
       </c>
       <c r="E60">
-        <v>-24.71573393947126</v>
+        <v>-19.49699369575973</v>
       </c>
       <c r="F60">
-        <v>-0.9855360850895512</v>
+        <v>-0.8533069352388076</v>
       </c>
       <c r="G60">
-        <v>-1.147194564755361</v>
+        <v>-1.238459684181989</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>3.729363000456211</v>
       </c>
       <c r="E61">
-        <v>-22.4264137181076</v>
+        <v>-18.8845085292743</v>
       </c>
       <c r="F61">
-        <v>-0.5351966383870208</v>
+        <v>-1.419641754305869</v>
       </c>
       <c r="G61">
-        <v>0.2490147742501055</v>
+        <v>-0.2504505418052778</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>3.639179392682855</v>
       </c>
       <c r="E62">
-        <v>-24.24737651522796</v>
+        <v>-19.07284776325331</v>
       </c>
       <c r="F62">
-        <v>-0.6025096827639014</v>
+        <v>-0.3308669011770233</v>
       </c>
       <c r="G62">
-        <v>-0.9536335881652528</v>
+        <v>-0.9191178403728114</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>3.540073104853357</v>
       </c>
       <c r="E63">
-        <v>-22.59788891488204</v>
+        <v>-18.39722208367893</v>
       </c>
       <c r="F63">
-        <v>-0.3476320119978653</v>
+        <v>-1.411724808434588</v>
       </c>
       <c r="G63">
-        <v>-1.84459077751269</v>
+        <v>-1.764548407464191</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>3.436822236178312</v>
       </c>
       <c r="E64">
-        <v>-22.24240370527992</v>
+        <v>-18.68751538146663</v>
       </c>
       <c r="F64">
-        <v>-0.6760767818008523</v>
+        <v>-1.555955281712531</v>
       </c>
       <c r="G64">
-        <v>-2.553650042204871</v>
+        <v>-1.296314778026292</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>3.334055277799238</v>
       </c>
       <c r="E65">
-        <v>-22.09726611333409</v>
+        <v>-19.86942898357256</v>
       </c>
       <c r="F65">
-        <v>-0.6656599561420493</v>
+        <v>-1.229882111517915</v>
       </c>
       <c r="G65">
-        <v>-2.517757107468093</v>
+        <v>-1.533670961555418</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>3.234919787828864</v>
       </c>
       <c r="E66">
-        <v>-22.30555327531688</v>
+        <v>-17.47171067988729</v>
       </c>
       <c r="F66">
-        <v>-0.5706866960990611</v>
+        <v>-0.9815776121539103</v>
       </c>
       <c r="G66">
-        <v>-2.217325099779233</v>
+        <v>-1.026899271494863</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>3.140032608452908</v>
       </c>
       <c r="E67">
-        <v>-22.0967453388232</v>
+        <v>-18.51825460848193</v>
       </c>
       <c r="F67">
-        <v>-0.2296356272091761</v>
+        <v>-1.576042215691008</v>
       </c>
       <c r="G67">
-        <v>-2.256075035316402</v>
+        <v>-2.064838061694863</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>3.056641090459264</v>
       </c>
       <c r="E68">
-        <v>-22.14201649347788</v>
+        <v>-17.52117972994708</v>
       </c>
       <c r="F68">
-        <v>-0.9874230706877973</v>
+        <v>-0.8234596217034781</v>
       </c>
       <c r="G68">
-        <v>-2.325652770915264</v>
+        <v>-1.766465213331429</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>2.990115600428796</v>
       </c>
       <c r="E69">
-        <v>-21.2143495360586</v>
+        <v>-18.43065580727756</v>
       </c>
       <c r="F69">
-        <v>-0.7870090463537238</v>
+        <v>-1.160024843587881</v>
       </c>
       <c r="G69">
-        <v>-2.754815341898685</v>
+        <v>-2.160151978316019</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>2.943213611368063</v>
       </c>
       <c r="E70">
-        <v>-20.76245764330718</v>
+        <v>-17.56335340838051</v>
       </c>
       <c r="F70">
-        <v>-0.8999233188597678</v>
+        <v>-0.706333483315323</v>
       </c>
       <c r="G70">
-        <v>-3.303114515203857</v>
+        <v>-2.512072900777164</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>2.915769193324544</v>
       </c>
       <c r="E71">
-        <v>-22.12898354528381</v>
+        <v>-18.44488427260966</v>
       </c>
       <c r="F71">
-        <v>-1.430846473657604</v>
+        <v>-0.7421101917980577</v>
       </c>
       <c r="G71">
-        <v>-4.475110536471104</v>
+        <v>-2.891881858861129</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>2.913822338447817</v>
       </c>
       <c r="E72">
-        <v>-22.231825189998</v>
+        <v>-15.52848361303384</v>
       </c>
       <c r="F72">
-        <v>-0.6766389974008333</v>
+        <v>-1.811004784570393</v>
       </c>
       <c r="G72">
-        <v>-3.426319777993374</v>
+        <v>-3.492643247327133</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>2.939834779529798</v>
       </c>
       <c r="E73">
-        <v>-21.05077199795353</v>
+        <v>-16.46721363245387</v>
       </c>
       <c r="F73">
-        <v>-0.2578762710932923</v>
+        <v>-0.8605381364487042</v>
       </c>
       <c r="G73">
-        <v>-3.188000225712319</v>
+        <v>-2.469111951314042</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>2.992991247335802</v>
       </c>
       <c r="E74">
-        <v>-19.84133433082897</v>
+        <v>-17.30378127826085</v>
       </c>
       <c r="F74">
-        <v>-0.2214827091564938</v>
+        <v>-0.7081856273834294</v>
       </c>
       <c r="G74">
-        <v>-3.69951592753065</v>
+        <v>-1.512245110825255</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>3.069731855332424</v>
       </c>
       <c r="E75">
-        <v>-21.76867098238951</v>
+        <v>-18.65751424116581</v>
       </c>
       <c r="F75">
-        <v>-0.8712867484967918</v>
+        <v>-1.781147176946613</v>
       </c>
       <c r="G75">
-        <v>-3.081983315362699</v>
+        <v>-2.168577316713464</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>3.172652927823858</v>
       </c>
       <c r="E76">
-        <v>-21.13015161883398</v>
+        <v>-18.60910032554981</v>
       </c>
       <c r="F76">
-        <v>-0.848898689823182</v>
+        <v>-1.005886706102948</v>
       </c>
       <c r="G76">
-        <v>-3.435893875692946</v>
+        <v>-1.415593733806233</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>3.300345217095793</v>
       </c>
       <c r="E77">
-        <v>-21.2985429248092</v>
+        <v>-20.42765850297209</v>
       </c>
       <c r="F77">
-        <v>-0.4739333506071189</v>
+        <v>-1.529409995010893</v>
       </c>
       <c r="G77">
-        <v>-4.221807455079308</v>
+        <v>-2.257429048441963</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>3.447953699573898</v>
       </c>
       <c r="E78">
-        <v>-22.40135767142316</v>
+        <v>-17.12926294695325</v>
       </c>
       <c r="F78">
-        <v>-0.693334425161396</v>
+        <v>-1.160823031369262</v>
       </c>
       <c r="G78">
-        <v>-2.786056960152787</v>
+        <v>-2.274425389240582</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>3.609692393801733</v>
       </c>
       <c r="E79">
-        <v>-22.12186478414375</v>
+        <v>-19.49934850224372</v>
       </c>
       <c r="F79">
-        <v>-0.8118645188435882</v>
+        <v>-1.546864809757909</v>
       </c>
       <c r="G79">
-        <v>-4.574718230656695</v>
+        <v>-3.120335985435156</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>3.78592225603432</v>
       </c>
       <c r="E80">
-        <v>-22.23859525863947</v>
+        <v>-18.69839277603305</v>
       </c>
       <c r="F80">
-        <v>-0.6551504836871932</v>
+        <v>-1.438922581973387</v>
       </c>
       <c r="G80">
-        <v>-4.967531011618918</v>
+        <v>-3.008952680766376</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>3.972987789362479</v>
       </c>
       <c r="E81">
-        <v>-23.86892288545893</v>
+        <v>-21.07364079169226</v>
       </c>
       <c r="F81">
-        <v>-0.6202741120173856</v>
+        <v>-1.306129632816747</v>
       </c>
       <c r="G81">
-        <v>-3.651403769208422</v>
+        <v>-2.553550725838693</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>4.163999145877241</v>
       </c>
       <c r="E82">
-        <v>-23.3928761123506</v>
+        <v>-21.35328311861392</v>
       </c>
       <c r="F82">
-        <v>-1.452752293879962</v>
+        <v>-1.587360961868653</v>
       </c>
       <c r="G82">
-        <v>-2.90564379666788</v>
+        <v>-2.64872891009274</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>4.353923043421839</v>
       </c>
       <c r="E83">
-        <v>-22.91986794530141</v>
+        <v>-21.26110603018779</v>
       </c>
       <c r="F83">
-        <v>-1.438223375811721</v>
+        <v>-1.759583437201989</v>
       </c>
       <c r="G83">
-        <v>-4.400437871287303</v>
+        <v>-2.824280518949212</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>4.542546593522738</v>
       </c>
       <c r="E84">
-        <v>-25.6117287496809</v>
+        <v>-21.38111964833907</v>
       </c>
       <c r="F84">
-        <v>-1.207183646484879</v>
+        <v>-1.90959681263016</v>
       </c>
       <c r="G84">
-        <v>-2.606509522830414</v>
+        <v>-3.594713987393942</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>4.726102048603219</v>
       </c>
       <c r="E85">
-        <v>-25.97793738573319</v>
+        <v>-23.24510747700631</v>
       </c>
       <c r="F85">
-        <v>-1.073368415159823</v>
+        <v>-1.940912221549102</v>
       </c>
       <c r="G85">
-        <v>-3.566392270305477</v>
+        <v>-1.928963341126555</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>4.896699691538446</v>
       </c>
       <c r="E86">
-        <v>-24.95142742614848</v>
+        <v>-23.55903035216603</v>
       </c>
       <c r="F86">
-        <v>-1.341352044229078</v>
+        <v>-1.860606453841956</v>
       </c>
       <c r="G86">
-        <v>-3.813077571164269</v>
+        <v>-3.223485963347767</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>5.049244110524953</v>
       </c>
       <c r="E87">
-        <v>-27.65874844079016</v>
+        <v>-24.96211915328059</v>
       </c>
       <c r="F87">
-        <v>-1.255169143869737</v>
+        <v>-1.209400042913537</v>
       </c>
       <c r="G87">
-        <v>-4.44864272488463</v>
+        <v>-2.261385150361393</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>5.180513493303714</v>
       </c>
       <c r="E88">
-        <v>-27.90676390524225</v>
+        <v>-27.30375683485487</v>
       </c>
       <c r="F88">
-        <v>-1.035209812980267</v>
+        <v>-1.546276463010323</v>
       </c>
       <c r="G88">
-        <v>-4.422694668947822</v>
+        <v>-3.517280327230389</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>5.283416321539043</v>
       </c>
       <c r="E89">
-        <v>-30.03253602358189</v>
+        <v>-28.71097560426443</v>
       </c>
       <c r="F89">
-        <v>-1.573444937989687</v>
+        <v>-2.137763699426394</v>
       </c>
       <c r="G89">
-        <v>-3.877116764075931</v>
+        <v>-3.411488533977439</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>5.346969533159633</v>
       </c>
       <c r="E90">
-        <v>-31.30837696931792</v>
+        <v>-30.16499841678026</v>
       </c>
       <c r="F90">
-        <v>-1.204166686715967</v>
+        <v>-2.630204384184967</v>
       </c>
       <c r="G90">
-        <v>-2.987295091848464</v>
+        <v>-1.935842654757161</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.363440822011276</v>
       </c>
       <c r="E91">
-        <v>-33.69729644800629</v>
+        <v>-31.26587950499294</v>
       </c>
       <c r="F91">
-        <v>-1.258151262108509</v>
+        <v>-1.704202825044987</v>
       </c>
       <c r="G91">
-        <v>-4.749270054760308</v>
+        <v>-2.76932877354285</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.325506903803255</v>
       </c>
       <c r="E92">
-        <v>-34.44583961605218</v>
+        <v>-31.57625432076765</v>
       </c>
       <c r="F92">
-        <v>-1.074214905971625</v>
+        <v>-1.852672879058562</v>
       </c>
       <c r="G92">
-        <v>-4.383527604672706</v>
+        <v>-2.528562728108274</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>5.223065328590119</v>
       </c>
       <c r="E93">
-        <v>-35.59455497520788</v>
+        <v>-36.00237123044264</v>
       </c>
       <c r="F93">
-        <v>-1.408275496950761</v>
+        <v>-1.588461637479884</v>
       </c>
       <c r="G93">
-        <v>-3.97101376720628</v>
+        <v>-2.938686351695345</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>5.044735148704038</v>
       </c>
       <c r="E94">
-        <v>-37.78831307382467</v>
+        <v>-34.87088897912313</v>
       </c>
       <c r="F94">
-        <v>-1.516096571232751</v>
+        <v>-1.591440588306825</v>
       </c>
       <c r="G94">
-        <v>-2.947270596278676</v>
+        <v>-3.050768181472911</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.785455665976399</v>
       </c>
       <c r="E95">
-        <v>-40.91494587496959</v>
+        <v>-39.32249214051328</v>
       </c>
       <c r="F95">
-        <v>-1.625627256050459</v>
+        <v>-2.367682956818062</v>
       </c>
       <c r="G95">
-        <v>-3.793959170674978</v>
+        <v>-3.192651542194995</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.435379368091905</v>
       </c>
       <c r="E96">
-        <v>-42.26228689681272</v>
+        <v>-40.71799121919098</v>
       </c>
       <c r="F96">
-        <v>-1.203819855120486</v>
+        <v>-2.146202476396813</v>
       </c>
       <c r="G96">
-        <v>-4.072915669450587</v>
+        <v>-4.353126864985578</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.99981359820723</v>
       </c>
       <c r="E97">
-        <v>-44.23349766879657</v>
+        <v>-43.86096049031857</v>
       </c>
       <c r="F97">
-        <v>-1.319035252321663</v>
+        <v>-1.151076905165648</v>
       </c>
       <c r="G97">
-        <v>-4.108801983096286</v>
+        <v>-3.26857890413818</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>3.460171342648296</v>
       </c>
       <c r="E98">
-        <v>-46.86077564111567</v>
+        <v>-44.70857308423026</v>
       </c>
       <c r="F98">
-        <v>-1.470077244741912</v>
+        <v>-2.504892861772863</v>
       </c>
       <c r="G98">
-        <v>-4.752928207581202</v>
+        <v>-3.237231348426821</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.848106988385634</v>
       </c>
       <c r="E99">
-        <v>-49.34306093265718</v>
+        <v>-45.95349587367892</v>
       </c>
       <c r="F99">
-        <v>-1.261545935738253</v>
+        <v>-2.596277444211466</v>
       </c>
       <c r="G99">
-        <v>-5.127241660069978</v>
+        <v>-5.572764947108476</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>2.132856302207269</v>
       </c>
       <c r="E100">
-        <v>-51.46303434003001</v>
+        <v>-48.69661787170674</v>
       </c>
       <c r="F100">
-        <v>-1.30424660648329</v>
+        <v>-2.389160384590295</v>
       </c>
       <c r="G100">
-        <v>-4.798514419656967</v>
+        <v>-3.608929469939572</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.390701486931577</v>
       </c>
       <c r="E101">
-        <v>-52.63780201015184</v>
+        <v>-51.83592700371761</v>
       </c>
       <c r="F101">
-        <v>-2.367618024875529</v>
+        <v>-2.555556405860729</v>
       </c>
       <c r="G101">
-        <v>-5.138908022550369</v>
+        <v>-5.059117253962855</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.5252058193000427</v>
       </c>
       <c r="E102">
-        <v>-55.71413478625654</v>
+        <v>-53.51226958704751</v>
       </c>
       <c r="F102">
-        <v>-1.517101432636098</v>
+        <v>-1.505860288048309</v>
       </c>
       <c r="G102">
-        <v>-4.846182964876932</v>
+        <v>-5.184394918259955</v>
       </c>
     </row>
   </sheetData>
